--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Mistral-7B-Instruct-v0.3/metrics_default_vs_simple.xlsx
@@ -420,25 +420,25 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>0.5882352941176471</v>
+        <v>0.6190476190476191</v>
       </c>
       <c r="B2">
-        <v>0.04444444444444445</v>
+        <v>0.02272727272727273</v>
       </c>
       <c r="C2">
-        <v>0.5492957746478874</v>
+        <v>0.5845070422535211</v>
       </c>
       <c r="D2">
-        <v>0.6666666666666666</v>
+        <v>0.686046511627907</v>
       </c>
       <c r="E2">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="F2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G2">
-        <v>46</v>
+        <v>56</v>
       </c>
     </row>
   </sheetData>
